--- a/downloads/purchasing/dixani-purchase-tracker.xlsx
+++ b/downloads/purchasing/dixani-purchase-tracker.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Tracker" sheetId="1" r:id="R199c6b6b4a874b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R57491877960044d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="3" r:id="Rc61322e84fe141ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="4" r:id="R0ede47a1d5634907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Tracker" sheetId="1" r:id="Re8fc9d93baa741b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R32e54c7dfef24d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="3" r:id="R59c1d93c348e41f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="4" r:id="R44fc4821f3224e04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -220,7 +220,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -231,7 +231,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -242,7 +242,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -253,7 +253,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -264,7 +264,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -344,9 +344,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -456,9 +454,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -523,7 +519,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcefa63a54a5e478b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdbef0f4c43f84201"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -553,7 +549,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rafb4de8b39be43a0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Refe48f21ae4f46bc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -956,7 +952,9 @@
       <x:c r="H6" s="31"/>
       <x:c r="I6" s="30"/>
       <x:c r="J6" s="30"/>
-      <x:c r="K6" s="30"/>
+      <x:c r="K6" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L6" s="32"/>
       <x:c r="M6" s="31"/>
       <x:c r="N6" s="31"/>
@@ -984,7 +982,9 @@
       <x:c r="H7" s="31"/>
       <x:c r="I7" s="30"/>
       <x:c r="J7" s="30"/>
-      <x:c r="K7" s="30"/>
+      <x:c r="K7" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L7" s="32"/>
       <x:c r="M7" s="31"/>
       <x:c r="N7" s="31"/>
@@ -1012,7 +1012,9 @@
       <x:c r="H8" s="31"/>
       <x:c r="I8" s="30"/>
       <x:c r="J8" s="30"/>
-      <x:c r="K8" s="30"/>
+      <x:c r="K8" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L8" s="32"/>
       <x:c r="M8" s="31"/>
       <x:c r="N8" s="31"/>
@@ -1040,7 +1042,9 @@
       <x:c r="H9" s="31"/>
       <x:c r="I9" s="30"/>
       <x:c r="J9" s="30"/>
-      <x:c r="K9" s="30"/>
+      <x:c r="K9" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L9" s="32"/>
       <x:c r="M9" s="31"/>
       <x:c r="N9" s="31"/>
@@ -1068,7 +1072,9 @@
       <x:c r="H10" s="31"/>
       <x:c r="I10" s="30"/>
       <x:c r="J10" s="30"/>
-      <x:c r="K10" s="30"/>
+      <x:c r="K10" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L10" s="32"/>
       <x:c r="M10" s="31"/>
       <x:c r="N10" s="31"/>
@@ -1096,7 +1102,9 @@
       <x:c r="H11" s="31"/>
       <x:c r="I11" s="30"/>
       <x:c r="J11" s="30"/>
-      <x:c r="K11" s="30"/>
+      <x:c r="K11" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L11" s="32"/>
       <x:c r="M11" s="31"/>
       <x:c r="N11" s="31"/>
@@ -1124,7 +1132,9 @@
       <x:c r="H12" s="31"/>
       <x:c r="I12" s="30"/>
       <x:c r="J12" s="30"/>
-      <x:c r="K12" s="30"/>
+      <x:c r="K12" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L12" s="32"/>
       <x:c r="M12" s="31"/>
       <x:c r="N12" s="31"/>
@@ -1152,7 +1162,9 @@
       <x:c r="H13" s="31"/>
       <x:c r="I13" s="30"/>
       <x:c r="J13" s="30"/>
-      <x:c r="K13" s="30"/>
+      <x:c r="K13" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L13" s="32"/>
       <x:c r="M13" s="31"/>
       <x:c r="N13" s="31"/>
@@ -1180,7 +1192,9 @@
       <x:c r="H14" s="31"/>
       <x:c r="I14" s="30"/>
       <x:c r="J14" s="30"/>
-      <x:c r="K14" s="30"/>
+      <x:c r="K14" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L14" s="32"/>
       <x:c r="M14" s="31"/>
       <x:c r="N14" s="31"/>
@@ -1208,7 +1222,9 @@
       <x:c r="H15" s="31"/>
       <x:c r="I15" s="30"/>
       <x:c r="J15" s="30"/>
-      <x:c r="K15" s="30"/>
+      <x:c r="K15" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L15" s="32"/>
       <x:c r="M15" s="31"/>
       <x:c r="N15" s="31"/>
@@ -1236,7 +1252,9 @@
       <x:c r="H16" s="31"/>
       <x:c r="I16" s="30"/>
       <x:c r="J16" s="30"/>
-      <x:c r="K16" s="30"/>
+      <x:c r="K16" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L16" s="32"/>
       <x:c r="M16" s="31"/>
       <x:c r="N16" s="31"/>
@@ -1264,7 +1282,9 @@
       <x:c r="H17" s="31"/>
       <x:c r="I17" s="30"/>
       <x:c r="J17" s="30"/>
-      <x:c r="K17" s="30"/>
+      <x:c r="K17" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L17" s="32"/>
       <x:c r="M17" s="31"/>
       <x:c r="N17" s="31"/>
@@ -1292,7 +1312,9 @@
       <x:c r="H18" s="31"/>
       <x:c r="I18" s="30"/>
       <x:c r="J18" s="30"/>
-      <x:c r="K18" s="30"/>
+      <x:c r="K18" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L18" s="32"/>
       <x:c r="M18" s="31"/>
       <x:c r="N18" s="31"/>
@@ -1320,7 +1342,9 @@
       <x:c r="H19" s="31"/>
       <x:c r="I19" s="30"/>
       <x:c r="J19" s="30"/>
-      <x:c r="K19" s="30"/>
+      <x:c r="K19" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L19" s="32"/>
       <x:c r="M19" s="31"/>
       <x:c r="N19" s="31"/>
@@ -1348,7 +1372,9 @@
       <x:c r="H20" s="31"/>
       <x:c r="I20" s="30"/>
       <x:c r="J20" s="30"/>
-      <x:c r="K20" s="30"/>
+      <x:c r="K20" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L20" s="32"/>
       <x:c r="M20" s="31"/>
       <x:c r="N20" s="31"/>
@@ -1376,7 +1402,9 @@
       <x:c r="H21" s="31"/>
       <x:c r="I21" s="30"/>
       <x:c r="J21" s="30"/>
-      <x:c r="K21" s="30"/>
+      <x:c r="K21" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L21" s="32"/>
       <x:c r="M21" s="31"/>
       <x:c r="N21" s="31"/>
@@ -1404,7 +1432,9 @@
       <x:c r="H22" s="31"/>
       <x:c r="I22" s="30"/>
       <x:c r="J22" s="30"/>
-      <x:c r="K22" s="30"/>
+      <x:c r="K22" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L22" s="32"/>
       <x:c r="M22" s="31"/>
       <x:c r="N22" s="31"/>
@@ -1432,7 +1462,9 @@
       <x:c r="H23" s="31"/>
       <x:c r="I23" s="30"/>
       <x:c r="J23" s="30"/>
-      <x:c r="K23" s="30"/>
+      <x:c r="K23" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L23" s="32"/>
       <x:c r="M23" s="31"/>
       <x:c r="N23" s="31"/>
@@ -1460,7 +1492,9 @@
       <x:c r="H24" s="31"/>
       <x:c r="I24" s="30"/>
       <x:c r="J24" s="30"/>
-      <x:c r="K24" s="30"/>
+      <x:c r="K24" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L24" s="32"/>
       <x:c r="M24" s="31"/>
       <x:c r="N24" s="31"/>
@@ -1488,7 +1522,9 @@
       <x:c r="H25" s="31"/>
       <x:c r="I25" s="30"/>
       <x:c r="J25" s="30"/>
-      <x:c r="K25" s="30"/>
+      <x:c r="K25" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L25" s="32"/>
       <x:c r="M25" s="31"/>
       <x:c r="N25" s="31"/>
@@ -1516,7 +1552,9 @@
       <x:c r="H26" s="31"/>
       <x:c r="I26" s="30"/>
       <x:c r="J26" s="30"/>
-      <x:c r="K26" s="30"/>
+      <x:c r="K26" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L26" s="32"/>
       <x:c r="M26" s="31"/>
       <x:c r="N26" s="31"/>
@@ -1544,7 +1582,9 @@
       <x:c r="H27" s="31"/>
       <x:c r="I27" s="30"/>
       <x:c r="J27" s="30"/>
-      <x:c r="K27" s="30"/>
+      <x:c r="K27" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L27" s="32"/>
       <x:c r="M27" s="31"/>
       <x:c r="N27" s="31"/>
@@ -1572,7 +1612,9 @@
       <x:c r="H28" s="31"/>
       <x:c r="I28" s="30"/>
       <x:c r="J28" s="30"/>
-      <x:c r="K28" s="30"/>
+      <x:c r="K28" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L28" s="32"/>
       <x:c r="M28" s="31"/>
       <x:c r="N28" s="31"/>
@@ -1600,7 +1642,9 @@
       <x:c r="H29" s="31"/>
       <x:c r="I29" s="30"/>
       <x:c r="J29" s="30"/>
-      <x:c r="K29" s="30"/>
+      <x:c r="K29" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L29" s="32"/>
       <x:c r="M29" s="31"/>
       <x:c r="N29" s="31"/>
@@ -1628,7 +1672,9 @@
       <x:c r="H30" s="31"/>
       <x:c r="I30" s="30"/>
       <x:c r="J30" s="30"/>
-      <x:c r="K30" s="30"/>
+      <x:c r="K30" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L30" s="32"/>
       <x:c r="M30" s="31"/>
       <x:c r="N30" s="31"/>
@@ -1656,7 +1702,9 @@
       <x:c r="H31" s="31"/>
       <x:c r="I31" s="30"/>
       <x:c r="J31" s="30"/>
-      <x:c r="K31" s="30"/>
+      <x:c r="K31" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L31" s="32"/>
       <x:c r="M31" s="31"/>
       <x:c r="N31" s="31"/>
@@ -1684,7 +1732,9 @@
       <x:c r="H32" s="31"/>
       <x:c r="I32" s="30"/>
       <x:c r="J32" s="30"/>
-      <x:c r="K32" s="30"/>
+      <x:c r="K32" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L32" s="32"/>
       <x:c r="M32" s="31"/>
       <x:c r="N32" s="31"/>
@@ -1712,7 +1762,9 @@
       <x:c r="H33" s="31"/>
       <x:c r="I33" s="30"/>
       <x:c r="J33" s="30"/>
-      <x:c r="K33" s="30"/>
+      <x:c r="K33" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L33" s="32"/>
       <x:c r="M33" s="31"/>
       <x:c r="N33" s="31"/>
@@ -1740,7 +1792,9 @@
       <x:c r="H34" s="31"/>
       <x:c r="I34" s="30"/>
       <x:c r="J34" s="30"/>
-      <x:c r="K34" s="30"/>
+      <x:c r="K34" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L34" s="32"/>
       <x:c r="M34" s="31"/>
       <x:c r="N34" s="31"/>
@@ -1768,7 +1822,9 @@
       <x:c r="H35" s="31"/>
       <x:c r="I35" s="30"/>
       <x:c r="J35" s="30"/>
-      <x:c r="K35" s="30"/>
+      <x:c r="K35" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L35" s="32"/>
       <x:c r="M35" s="31"/>
       <x:c r="N35" s="31"/>
@@ -1796,7 +1852,9 @@
       <x:c r="H36" s="31"/>
       <x:c r="I36" s="30"/>
       <x:c r="J36" s="30"/>
-      <x:c r="K36" s="30"/>
+      <x:c r="K36" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L36" s="32"/>
       <x:c r="M36" s="31"/>
       <x:c r="N36" s="31"/>
@@ -1824,7 +1882,9 @@
       <x:c r="H37" s="31"/>
       <x:c r="I37" s="30"/>
       <x:c r="J37" s="30"/>
-      <x:c r="K37" s="30"/>
+      <x:c r="K37" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L37" s="32"/>
       <x:c r="M37" s="31"/>
       <x:c r="N37" s="31"/>
@@ -1852,7 +1912,9 @@
       <x:c r="H38" s="31"/>
       <x:c r="I38" s="30"/>
       <x:c r="J38" s="30"/>
-      <x:c r="K38" s="30"/>
+      <x:c r="K38" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L38" s="32"/>
       <x:c r="M38" s="31"/>
       <x:c r="N38" s="31"/>
@@ -1880,7 +1942,9 @@
       <x:c r="H39" s="31"/>
       <x:c r="I39" s="30"/>
       <x:c r="J39" s="30"/>
-      <x:c r="K39" s="30"/>
+      <x:c r="K39" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L39" s="32"/>
       <x:c r="M39" s="31"/>
       <x:c r="N39" s="31"/>
@@ -1908,7 +1972,9 @@
       <x:c r="H40" s="31"/>
       <x:c r="I40" s="30"/>
       <x:c r="J40" s="30"/>
-      <x:c r="K40" s="30"/>
+      <x:c r="K40" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L40" s="32"/>
       <x:c r="M40" s="31"/>
       <x:c r="N40" s="31"/>
@@ -1936,7 +2002,9 @@
       <x:c r="H41" s="31"/>
       <x:c r="I41" s="30"/>
       <x:c r="J41" s="30"/>
-      <x:c r="K41" s="30"/>
+      <x:c r="K41" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L41" s="32"/>
       <x:c r="M41" s="31"/>
       <x:c r="N41" s="31"/>
@@ -1964,7 +2032,9 @@
       <x:c r="H42" s="31"/>
       <x:c r="I42" s="30"/>
       <x:c r="J42" s="30"/>
-      <x:c r="K42" s="30"/>
+      <x:c r="K42" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L42" s="32"/>
       <x:c r="M42" s="31"/>
       <x:c r="N42" s="31"/>
@@ -1992,7 +2062,9 @@
       <x:c r="H43" s="31"/>
       <x:c r="I43" s="30"/>
       <x:c r="J43" s="30"/>
-      <x:c r="K43" s="30"/>
+      <x:c r="K43" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L43" s="32"/>
       <x:c r="M43" s="31"/>
       <x:c r="N43" s="31"/>
@@ -2020,7 +2092,9 @@
       <x:c r="H44" s="31"/>
       <x:c r="I44" s="30"/>
       <x:c r="J44" s="30"/>
-      <x:c r="K44" s="30"/>
+      <x:c r="K44" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L44" s="32"/>
       <x:c r="M44" s="31"/>
       <x:c r="N44" s="31"/>
@@ -2048,7 +2122,9 @@
       <x:c r="H45" s="31"/>
       <x:c r="I45" s="30"/>
       <x:c r="J45" s="30"/>
-      <x:c r="K45" s="30"/>
+      <x:c r="K45" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L45" s="32"/>
       <x:c r="M45" s="31"/>
       <x:c r="N45" s="31"/>
@@ -2076,7 +2152,9 @@
       <x:c r="H46" s="31"/>
       <x:c r="I46" s="30"/>
       <x:c r="J46" s="30"/>
-      <x:c r="K46" s="30"/>
+      <x:c r="K46" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L46" s="32"/>
       <x:c r="M46" s="31"/>
       <x:c r="N46" s="31"/>
@@ -2104,7 +2182,9 @@
       <x:c r="H47" s="31"/>
       <x:c r="I47" s="30"/>
       <x:c r="J47" s="30"/>
-      <x:c r="K47" s="30"/>
+      <x:c r="K47" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L47" s="32"/>
       <x:c r="M47" s="31"/>
       <x:c r="N47" s="31"/>
@@ -2132,7 +2212,9 @@
       <x:c r="H48" s="31"/>
       <x:c r="I48" s="30"/>
       <x:c r="J48" s="30"/>
-      <x:c r="K48" s="30"/>
+      <x:c r="K48" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L48" s="32"/>
       <x:c r="M48" s="31"/>
       <x:c r="N48" s="31"/>
@@ -2160,7 +2242,9 @@
       <x:c r="H49" s="31"/>
       <x:c r="I49" s="30"/>
       <x:c r="J49" s="30"/>
-      <x:c r="K49" s="30"/>
+      <x:c r="K49" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L49" s="32"/>
       <x:c r="M49" s="31"/>
       <x:c r="N49" s="31"/>
@@ -2188,7 +2272,9 @@
       <x:c r="H50" s="31"/>
       <x:c r="I50" s="30"/>
       <x:c r="J50" s="30"/>
-      <x:c r="K50" s="30"/>
+      <x:c r="K50" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L50" s="32"/>
       <x:c r="M50" s="31"/>
       <x:c r="N50" s="31"/>
@@ -2216,7 +2302,9 @@
       <x:c r="H51" s="31"/>
       <x:c r="I51" s="30"/>
       <x:c r="J51" s="30"/>
-      <x:c r="K51" s="30"/>
+      <x:c r="K51" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L51" s="32"/>
       <x:c r="M51" s="31"/>
       <x:c r="N51" s="31"/>
@@ -2244,7 +2332,9 @@
       <x:c r="H52" s="31"/>
       <x:c r="I52" s="30"/>
       <x:c r="J52" s="30"/>
-      <x:c r="K52" s="30"/>
+      <x:c r="K52" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L52" s="32"/>
       <x:c r="M52" s="31"/>
       <x:c r="N52" s="31"/>
@@ -2272,7 +2362,9 @@
       <x:c r="H53" s="31"/>
       <x:c r="I53" s="30"/>
       <x:c r="J53" s="30"/>
-      <x:c r="K53" s="30"/>
+      <x:c r="K53" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L53" s="32"/>
       <x:c r="M53" s="31"/>
       <x:c r="N53" s="31"/>
@@ -2300,7 +2392,9 @@
       <x:c r="H54" s="31"/>
       <x:c r="I54" s="30"/>
       <x:c r="J54" s="30"/>
-      <x:c r="K54" s="30"/>
+      <x:c r="K54" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L54" s="32"/>
       <x:c r="M54" s="31"/>
       <x:c r="N54" s="31"/>
@@ -2328,7 +2422,9 @@
       <x:c r="H55" s="31"/>
       <x:c r="I55" s="30"/>
       <x:c r="J55" s="30"/>
-      <x:c r="K55" s="30"/>
+      <x:c r="K55" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L55" s="32"/>
       <x:c r="M55" s="31"/>
       <x:c r="N55" s="31"/>
@@ -2356,7 +2452,9 @@
       <x:c r="H56" s="31"/>
       <x:c r="I56" s="30"/>
       <x:c r="J56" s="30"/>
-      <x:c r="K56" s="30"/>
+      <x:c r="K56" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L56" s="32"/>
       <x:c r="M56" s="31"/>
       <x:c r="N56" s="31"/>
@@ -2384,7 +2482,9 @@
       <x:c r="H57" s="31"/>
       <x:c r="I57" s="30"/>
       <x:c r="J57" s="30"/>
-      <x:c r="K57" s="30"/>
+      <x:c r="K57" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L57" s="32"/>
       <x:c r="M57" s="31"/>
       <x:c r="N57" s="31"/>
@@ -2412,7 +2512,9 @@
       <x:c r="H58" s="31"/>
       <x:c r="I58" s="30"/>
       <x:c r="J58" s="30"/>
-      <x:c r="K58" s="30"/>
+      <x:c r="K58" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L58" s="32"/>
       <x:c r="M58" s="31"/>
       <x:c r="N58" s="31"/>
@@ -2440,7 +2542,9 @@
       <x:c r="H59" s="31"/>
       <x:c r="I59" s="30"/>
       <x:c r="J59" s="30"/>
-      <x:c r="K59" s="30"/>
+      <x:c r="K59" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L59" s="32"/>
       <x:c r="M59" s="31"/>
       <x:c r="N59" s="31"/>
@@ -2468,7 +2572,9 @@
       <x:c r="H60" s="31"/>
       <x:c r="I60" s="30"/>
       <x:c r="J60" s="30"/>
-      <x:c r="K60" s="30"/>
+      <x:c r="K60" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L60" s="32"/>
       <x:c r="M60" s="31"/>
       <x:c r="N60" s="31"/>
@@ -2496,7 +2602,9 @@
       <x:c r="H61" s="31"/>
       <x:c r="I61" s="30"/>
       <x:c r="J61" s="30"/>
-      <x:c r="K61" s="30"/>
+      <x:c r="K61" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L61" s="32"/>
       <x:c r="M61" s="31"/>
       <x:c r="N61" s="31"/>
@@ -2524,7 +2632,9 @@
       <x:c r="H62" s="31"/>
       <x:c r="I62" s="30"/>
       <x:c r="J62" s="30"/>
-      <x:c r="K62" s="30"/>
+      <x:c r="K62" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L62" s="32"/>
       <x:c r="M62" s="31"/>
       <x:c r="N62" s="31"/>
@@ -2552,7 +2662,9 @@
       <x:c r="H63" s="31"/>
       <x:c r="I63" s="30"/>
       <x:c r="J63" s="30"/>
-      <x:c r="K63" s="30"/>
+      <x:c r="K63" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L63" s="32"/>
       <x:c r="M63" s="31"/>
       <x:c r="N63" s="31"/>
@@ -2580,7 +2692,9 @@
       <x:c r="H64" s="31"/>
       <x:c r="I64" s="30"/>
       <x:c r="J64" s="30"/>
-      <x:c r="K64" s="30"/>
+      <x:c r="K64" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L64" s="32"/>
       <x:c r="M64" s="31"/>
       <x:c r="N64" s="31"/>
@@ -2608,7 +2722,9 @@
       <x:c r="H65" s="31"/>
       <x:c r="I65" s="30"/>
       <x:c r="J65" s="30"/>
-      <x:c r="K65" s="30"/>
+      <x:c r="K65" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L65" s="32"/>
       <x:c r="M65" s="31"/>
       <x:c r="N65" s="31"/>
@@ -2636,7 +2752,9 @@
       <x:c r="H66" s="31"/>
       <x:c r="I66" s="30"/>
       <x:c r="J66" s="30"/>
-      <x:c r="K66" s="30"/>
+      <x:c r="K66" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L66" s="32"/>
       <x:c r="M66" s="31"/>
       <x:c r="N66" s="31"/>
@@ -2664,7 +2782,9 @@
       <x:c r="H67" s="31"/>
       <x:c r="I67" s="30"/>
       <x:c r="J67" s="30"/>
-      <x:c r="K67" s="30"/>
+      <x:c r="K67" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L67" s="32"/>
       <x:c r="M67" s="31"/>
       <x:c r="N67" s="31"/>
@@ -2692,7 +2812,9 @@
       <x:c r="H68" s="31"/>
       <x:c r="I68" s="30"/>
       <x:c r="J68" s="30"/>
-      <x:c r="K68" s="30"/>
+      <x:c r="K68" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L68" s="32"/>
       <x:c r="M68" s="31"/>
       <x:c r="N68" s="31"/>
@@ -2720,7 +2842,9 @@
       <x:c r="H69" s="31"/>
       <x:c r="I69" s="30"/>
       <x:c r="J69" s="30"/>
-      <x:c r="K69" s="30"/>
+      <x:c r="K69" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L69" s="32"/>
       <x:c r="M69" s="31"/>
       <x:c r="N69" s="31"/>
@@ -2748,7 +2872,9 @@
       <x:c r="H70" s="31"/>
       <x:c r="I70" s="30"/>
       <x:c r="J70" s="30"/>
-      <x:c r="K70" s="30"/>
+      <x:c r="K70" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L70" s="32"/>
       <x:c r="M70" s="31"/>
       <x:c r="N70" s="31"/>
@@ -2776,7 +2902,9 @@
       <x:c r="H71" s="31"/>
       <x:c r="I71" s="30"/>
       <x:c r="J71" s="30"/>
-      <x:c r="K71" s="30"/>
+      <x:c r="K71" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L71" s="32"/>
       <x:c r="M71" s="31"/>
       <x:c r="N71" s="31"/>
@@ -2804,7 +2932,9 @@
       <x:c r="H72" s="31"/>
       <x:c r="I72" s="30"/>
       <x:c r="J72" s="30"/>
-      <x:c r="K72" s="30"/>
+      <x:c r="K72" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L72" s="32"/>
       <x:c r="M72" s="31"/>
       <x:c r="N72" s="31"/>
@@ -2832,7 +2962,9 @@
       <x:c r="H73" s="31"/>
       <x:c r="I73" s="30"/>
       <x:c r="J73" s="30"/>
-      <x:c r="K73" s="30"/>
+      <x:c r="K73" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L73" s="32"/>
       <x:c r="M73" s="31"/>
       <x:c r="N73" s="31"/>
@@ -2860,7 +2992,9 @@
       <x:c r="H74" s="31"/>
       <x:c r="I74" s="30"/>
       <x:c r="J74" s="30"/>
-      <x:c r="K74" s="30"/>
+      <x:c r="K74" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L74" s="32"/>
       <x:c r="M74" s="31"/>
       <x:c r="N74" s="31"/>
@@ -2888,7 +3022,9 @@
       <x:c r="H75" s="31"/>
       <x:c r="I75" s="30"/>
       <x:c r="J75" s="30"/>
-      <x:c r="K75" s="30"/>
+      <x:c r="K75" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L75" s="32"/>
       <x:c r="M75" s="31"/>
       <x:c r="N75" s="31"/>
@@ -2916,7 +3052,9 @@
       <x:c r="H76" s="31"/>
       <x:c r="I76" s="30"/>
       <x:c r="J76" s="30"/>
-      <x:c r="K76" s="30"/>
+      <x:c r="K76" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L76" s="32"/>
       <x:c r="M76" s="31"/>
       <x:c r="N76" s="31"/>
@@ -2944,7 +3082,9 @@
       <x:c r="H77" s="31"/>
       <x:c r="I77" s="30"/>
       <x:c r="J77" s="30"/>
-      <x:c r="K77" s="30"/>
+      <x:c r="K77" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L77" s="32"/>
       <x:c r="M77" s="31"/>
       <x:c r="N77" s="31"/>
@@ -2972,7 +3112,9 @@
       <x:c r="H78" s="31"/>
       <x:c r="I78" s="30"/>
       <x:c r="J78" s="30"/>
-      <x:c r="K78" s="30"/>
+      <x:c r="K78" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L78" s="32"/>
       <x:c r="M78" s="31"/>
       <x:c r="N78" s="31"/>
@@ -3000,7 +3142,9 @@
       <x:c r="H79" s="31"/>
       <x:c r="I79" s="30"/>
       <x:c r="J79" s="30"/>
-      <x:c r="K79" s="30"/>
+      <x:c r="K79" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L79" s="32"/>
       <x:c r="M79" s="31"/>
       <x:c r="N79" s="31"/>
@@ -3028,7 +3172,9 @@
       <x:c r="H80" s="31"/>
       <x:c r="I80" s="30"/>
       <x:c r="J80" s="30"/>
-      <x:c r="K80" s="30"/>
+      <x:c r="K80" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L80" s="32"/>
       <x:c r="M80" s="31"/>
       <x:c r="N80" s="31"/>
@@ -3056,7 +3202,9 @@
       <x:c r="H81" s="31"/>
       <x:c r="I81" s="30"/>
       <x:c r="J81" s="30"/>
-      <x:c r="K81" s="30"/>
+      <x:c r="K81" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L81" s="32"/>
       <x:c r="M81" s="31"/>
       <x:c r="N81" s="31"/>
@@ -3084,7 +3232,9 @@
       <x:c r="H82" s="31"/>
       <x:c r="I82" s="30"/>
       <x:c r="J82" s="30"/>
-      <x:c r="K82" s="30"/>
+      <x:c r="K82" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L82" s="32"/>
       <x:c r="M82" s="31"/>
       <x:c r="N82" s="31"/>
@@ -3112,7 +3262,9 @@
       <x:c r="H83" s="31"/>
       <x:c r="I83" s="30"/>
       <x:c r="J83" s="30"/>
-      <x:c r="K83" s="30"/>
+      <x:c r="K83" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L83" s="32"/>
       <x:c r="M83" s="31"/>
       <x:c r="N83" s="31"/>
@@ -3140,7 +3292,9 @@
       <x:c r="H84" s="31"/>
       <x:c r="I84" s="30"/>
       <x:c r="J84" s="30"/>
-      <x:c r="K84" s="30"/>
+      <x:c r="K84" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L84" s="32"/>
       <x:c r="M84" s="31"/>
       <x:c r="N84" s="31"/>
@@ -3168,7 +3322,9 @@
       <x:c r="H85" s="31"/>
       <x:c r="I85" s="30"/>
       <x:c r="J85" s="30"/>
-      <x:c r="K85" s="30"/>
+      <x:c r="K85" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L85" s="32"/>
       <x:c r="M85" s="31"/>
       <x:c r="N85" s="31"/>
@@ -3196,7 +3352,9 @@
       <x:c r="H86" s="31"/>
       <x:c r="I86" s="30"/>
       <x:c r="J86" s="30"/>
-      <x:c r="K86" s="30"/>
+      <x:c r="K86" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L86" s="32"/>
       <x:c r="M86" s="31"/>
       <x:c r="N86" s="31"/>
@@ -3224,7 +3382,9 @@
       <x:c r="H87" s="31"/>
       <x:c r="I87" s="30"/>
       <x:c r="J87" s="30"/>
-      <x:c r="K87" s="30"/>
+      <x:c r="K87" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L87" s="32"/>
       <x:c r="M87" s="31"/>
       <x:c r="N87" s="31"/>
@@ -3252,7 +3412,9 @@
       <x:c r="H88" s="31"/>
       <x:c r="I88" s="30"/>
       <x:c r="J88" s="30"/>
-      <x:c r="K88" s="30"/>
+      <x:c r="K88" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L88" s="32"/>
       <x:c r="M88" s="31"/>
       <x:c r="N88" s="31"/>
@@ -3280,7 +3442,9 @@
       <x:c r="H89" s="31"/>
       <x:c r="I89" s="30"/>
       <x:c r="J89" s="30"/>
-      <x:c r="K89" s="30"/>
+      <x:c r="K89" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L89" s="32"/>
       <x:c r="M89" s="31"/>
       <x:c r="N89" s="31"/>
@@ -3308,7 +3472,9 @@
       <x:c r="H90" s="31"/>
       <x:c r="I90" s="30"/>
       <x:c r="J90" s="30"/>
-      <x:c r="K90" s="30"/>
+      <x:c r="K90" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L90" s="32"/>
       <x:c r="M90" s="31"/>
       <x:c r="N90" s="31"/>
@@ -3336,7 +3502,9 @@
       <x:c r="H91" s="31"/>
       <x:c r="I91" s="30"/>
       <x:c r="J91" s="30"/>
-      <x:c r="K91" s="30"/>
+      <x:c r="K91" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L91" s="32"/>
       <x:c r="M91" s="31"/>
       <x:c r="N91" s="31"/>
@@ -3364,7 +3532,9 @@
       <x:c r="H92" s="31"/>
       <x:c r="I92" s="30"/>
       <x:c r="J92" s="30"/>
-      <x:c r="K92" s="30"/>
+      <x:c r="K92" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L92" s="32"/>
       <x:c r="M92" s="31"/>
       <x:c r="N92" s="31"/>
@@ -3392,7 +3562,9 @@
       <x:c r="H93" s="31"/>
       <x:c r="I93" s="30"/>
       <x:c r="J93" s="30"/>
-      <x:c r="K93" s="30"/>
+      <x:c r="K93" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L93" s="32"/>
       <x:c r="M93" s="31"/>
       <x:c r="N93" s="31"/>
@@ -3420,7 +3592,9 @@
       <x:c r="H94" s="31"/>
       <x:c r="I94" s="30"/>
       <x:c r="J94" s="30"/>
-      <x:c r="K94" s="30"/>
+      <x:c r="K94" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L94" s="32"/>
       <x:c r="M94" s="31"/>
       <x:c r="N94" s="31"/>
@@ -3448,7 +3622,9 @@
       <x:c r="H95" s="31"/>
       <x:c r="I95" s="30"/>
       <x:c r="J95" s="30"/>
-      <x:c r="K95" s="30"/>
+      <x:c r="K95" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L95" s="32"/>
       <x:c r="M95" s="31"/>
       <x:c r="N95" s="31"/>
@@ -3476,7 +3652,9 @@
       <x:c r="H96" s="31"/>
       <x:c r="I96" s="30"/>
       <x:c r="J96" s="30"/>
-      <x:c r="K96" s="30"/>
+      <x:c r="K96" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L96" s="32"/>
       <x:c r="M96" s="31"/>
       <x:c r="N96" s="31"/>
@@ -3504,7 +3682,9 @@
       <x:c r="H97" s="31"/>
       <x:c r="I97" s="30"/>
       <x:c r="J97" s="30"/>
-      <x:c r="K97" s="30"/>
+      <x:c r="K97" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L97" s="32"/>
       <x:c r="M97" s="31"/>
       <x:c r="N97" s="31"/>
@@ -3532,7 +3712,9 @@
       <x:c r="H98" s="31"/>
       <x:c r="I98" s="30"/>
       <x:c r="J98" s="30"/>
-      <x:c r="K98" s="30"/>
+      <x:c r="K98" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L98" s="32"/>
       <x:c r="M98" s="31"/>
       <x:c r="N98" s="31"/>
@@ -3560,7 +3742,9 @@
       <x:c r="H99" s="31"/>
       <x:c r="I99" s="30"/>
       <x:c r="J99" s="30"/>
-      <x:c r="K99" s="30"/>
+      <x:c r="K99" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L99" s="32"/>
       <x:c r="M99" s="31"/>
       <x:c r="N99" s="31"/>
@@ -3588,7 +3772,9 @@
       <x:c r="H100" s="31"/>
       <x:c r="I100" s="30"/>
       <x:c r="J100" s="30"/>
-      <x:c r="K100" s="30"/>
+      <x:c r="K100" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L100" s="32"/>
       <x:c r="M100" s="31"/>
       <x:c r="N100" s="31"/>
@@ -3616,7 +3802,9 @@
       <x:c r="H101" s="31"/>
       <x:c r="I101" s="30"/>
       <x:c r="J101" s="30"/>
-      <x:c r="K101" s="30"/>
+      <x:c r="K101" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L101" s="32"/>
       <x:c r="M101" s="31"/>
       <x:c r="N101" s="31"/>
@@ -3644,7 +3832,9 @@
       <x:c r="H102" s="31"/>
       <x:c r="I102" s="30"/>
       <x:c r="J102" s="30"/>
-      <x:c r="K102" s="30"/>
+      <x:c r="K102" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L102" s="32"/>
       <x:c r="M102" s="31"/>
       <x:c r="N102" s="31"/>
@@ -3672,7 +3862,9 @@
       <x:c r="H103" s="31"/>
       <x:c r="I103" s="30"/>
       <x:c r="J103" s="30"/>
-      <x:c r="K103" s="30"/>
+      <x:c r="K103" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L103" s="32"/>
       <x:c r="M103" s="31"/>
       <x:c r="N103" s="31"/>
@@ -3700,7 +3892,9 @@
       <x:c r="H104" s="31"/>
       <x:c r="I104" s="30"/>
       <x:c r="J104" s="30"/>
-      <x:c r="K104" s="30"/>
+      <x:c r="K104" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L104" s="32"/>
       <x:c r="M104" s="31"/>
       <x:c r="N104" s="31"/>
@@ -3728,7 +3922,9 @@
       <x:c r="H105" s="31"/>
       <x:c r="I105" s="30"/>
       <x:c r="J105" s="30"/>
-      <x:c r="K105" s="30"/>
+      <x:c r="K105" s="30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="L105" s="32"/>
       <x:c r="M105" s="31"/>
       <x:c r="N105" s="31"/>
@@ -3785,7 +3981,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="K6:K105">
-      <x:formula1>"QAR,USD,EUR,GBP,AED,SAR,LKR,INR"</x:formula1>
+      <x:formula1>"USD,EUR,GBP,CAD,AUD,NZD,CHF,JPY,CNY,HKD,SGD,INR,AED,SAR,QAR,LKR,ZAR,BRL,MXN"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="O6:O105">
       <x:formula1>"Not Ordered,Open,Partially Delivered,Delivered,Delayed,Cancelled,Closed"</x:formula1>
@@ -3802,7 +3998,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57a4a2b1d3894251"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabd0fa17d0274cc9"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3884,10 +4080,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="48" t="str">
-        <x:v>Total PO Value</x:v>
+        <x:v>PO Value (USD)</x:v>
       </x:c>
       <x:c r="D4" s="54" t="n">
-        <x:f>SUM('Purchase Tracker'!L6:L105)</x:f>
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,"USD",'Purchase Tracker'!L6:L105)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="48" t="str">
@@ -4024,7 +4220,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>QAR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="H9" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G9,'Purchase Tracker'!L6:L105)</x:f>
@@ -4054,7 +4250,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>USD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="H10" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G10,'Purchase Tracker'!L6:L105)</x:f>
@@ -4084,7 +4280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>EUR</x:v>
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="H11" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G11,'Purchase Tracker'!L6:L105)</x:f>
@@ -4114,7 +4310,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>GBP</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="H12" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G12,'Purchase Tracker'!L6:L105)</x:f>
@@ -4144,7 +4340,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>AED</x:v>
+        <x:v>AUD</x:v>
       </x:c>
       <x:c r="H13" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G13,'Purchase Tracker'!L6:L105)</x:f>
@@ -4167,7 +4363,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>SAR</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="H14" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G14,'Purchase Tracker'!L6:L105)</x:f>
@@ -4190,7 +4386,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>LKR</x:v>
+        <x:v>CHF</x:v>
       </x:c>
       <x:c r="H15" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G15,'Purchase Tracker'!L6:L105)</x:f>
@@ -4199,10 +4395,109 @@
     </x:row>
     <x:row r="16">
       <x:c r="G16" t="str">
-        <x:v>INR</x:v>
+        <x:v>JPY</x:v>
       </x:c>
       <x:c r="H16" s="26" t="n">
         <x:f>SUMIF('Purchase Tracker'!K6:K105,G16,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="G17" t="str">
+        <x:v>CNY</x:v>
+      </x:c>
+      <x:c r="H17" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G17,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="G18" t="str">
+        <x:v>HKD</x:v>
+      </x:c>
+      <x:c r="H18" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G18,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="G19" t="str">
+        <x:v>SGD</x:v>
+      </x:c>
+      <x:c r="H19" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G19,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="G20" t="str">
+        <x:v>INR</x:v>
+      </x:c>
+      <x:c r="H20" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G20,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="G21" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="H21" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G21,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="G22" t="str">
+        <x:v>SAR</x:v>
+      </x:c>
+      <x:c r="H22" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G22,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="G23" t="str">
+        <x:v>QAR</x:v>
+      </x:c>
+      <x:c r="H23" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G23,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="G24" t="str">
+        <x:v>LKR</x:v>
+      </x:c>
+      <x:c r="H24" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G24,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="G25" t="str">
+        <x:v>ZAR</x:v>
+      </x:c>
+      <x:c r="H25" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G25,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="G26" t="str">
+        <x:v>BRL</x:v>
+      </x:c>
+      <x:c r="H26" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G26,'Purchase Tracker'!L6:L105)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="G27" t="str">
+        <x:v>MXN</x:v>
+      </x:c>
+      <x:c r="H27" s="26" t="n">
+        <x:f>SUMIF('Purchase Tracker'!K6:K105,G27,'Purchase Tracker'!L6:L105)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4211,7 +4506,7 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf9a953007ca4bb4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R664c2c9bf66c4c55"/>
 </x:worksheet>
 </file>
 
@@ -4474,7 +4769,7 @@
         <x:v>Carton boxes 5-ply</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>QAR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="L2" s="26" t="n">
         <x:v>8500</x:v>
@@ -4548,7 +4843,7 @@
         <x:v>Hand pallet truck</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>QAR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="L3" s="26" t="n">
         <x:v>4200</x:v>
@@ -4612,7 +4907,7 @@
         <x:v>Printer toner and stationery</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>QAR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="L4" s="26" t="n">
         <x:v>1650</x:v>
